--- a/output/懲戒規程_いいかいご.xlsx
+++ b/output/懲戒規程_いいかいご.xlsx
@@ -825,7 +825,7 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>3　禁錮以上の刑に処せられ、その判決が確定した場合。</t>
+          <t>3　拘禁刑以上の刑に処せられ、その判決が確定した場合。</t>
         </is>
       </c>
     </row>
